--- a/Uploads/francais - error.xlsx
+++ b/Uploads/francais - error.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201FE278-167E-4FE9-8520-6B54F17EC02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5E1D6E-5ED9-4E62-8C94-8E7F2BBC0269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -646,9 +646,6 @@
     <t>610</t>
   </si>
   <si>
-    <t xml:space="preserve">Numero_Dossier </t>
-  </si>
-  <si>
     <t>Appelant</t>
   </si>
   <si>
@@ -794,6 +791,9 @@
   </si>
   <si>
     <t>Date_Reception_Comptable_Copie_Decision</t>
+  </si>
+  <si>
+    <t>Numero_Dossier</t>
   </si>
 </sst>
 </file>
@@ -1182,214 +1182,214 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" customWidth="1"/>
-    <col min="5" max="5" width="30.7265625" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" customWidth="1"/>
-    <col min="8" max="8" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="37.81640625" customWidth="1"/>
-    <col min="11" max="11" width="32.26953125" customWidth="1"/>
-    <col min="12" max="12" width="28.26953125" customWidth="1"/>
-    <col min="13" max="13" width="28.7265625" customWidth="1"/>
-    <col min="14" max="14" width="35.26953125" customWidth="1"/>
-    <col min="15" max="15" width="23.90625" customWidth="1"/>
-    <col min="16" max="16" width="26.26953125" customWidth="1"/>
-    <col min="17" max="17" width="47.81640625" customWidth="1"/>
-    <col min="18" max="18" width="36.54296875" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" customWidth="1"/>
+    <col min="11" max="11" width="32.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
+    <col min="13" max="13" width="28.7109375" customWidth="1"/>
+    <col min="14" max="14" width="35.28515625" customWidth="1"/>
+    <col min="15" max="15" width="23.85546875" customWidth="1"/>
+    <col min="16" max="16" width="26.28515625" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" customWidth="1"/>
+    <col min="18" max="18" width="36.5703125" customWidth="1"/>
     <col min="19" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="39.26953125" customWidth="1"/>
-    <col min="21" max="21" width="53.1796875" customWidth="1"/>
-    <col min="22" max="22" width="39.1796875" customWidth="1"/>
-    <col min="23" max="23" width="29.36328125" customWidth="1"/>
-    <col min="24" max="24" width="28.453125" customWidth="1"/>
-    <col min="25" max="25" width="50.08984375" customWidth="1"/>
-    <col min="26" max="26" width="37.90625" customWidth="1"/>
-    <col min="27" max="27" width="31.6328125" customWidth="1"/>
+    <col min="20" max="20" width="39.28515625" customWidth="1"/>
+    <col min="21" max="21" width="53.140625" customWidth="1"/>
+    <col min="22" max="22" width="39.140625" customWidth="1"/>
+    <col min="23" max="23" width="29.42578125" customWidth="1"/>
+    <col min="24" max="24" width="28.42578125" customWidth="1"/>
+    <col min="25" max="25" width="50.140625" customWidth="1"/>
+    <col min="26" max="26" width="37.85546875" customWidth="1"/>
+    <col min="27" max="27" width="31.5703125" customWidth="1"/>
     <col min="28" max="28" width="36" customWidth="1"/>
-    <col min="29" max="29" width="33.6328125" customWidth="1"/>
-    <col min="30" max="30" width="37.08984375" customWidth="1"/>
-    <col min="31" max="31" width="38.1796875" customWidth="1"/>
-    <col min="32" max="32" width="36.90625" customWidth="1"/>
-    <col min="33" max="33" width="49.26953125" customWidth="1"/>
-    <col min="34" max="34" width="42.453125" customWidth="1"/>
-    <col min="35" max="35" width="34.1796875" customWidth="1"/>
-    <col min="36" max="36" width="38.08984375" customWidth="1"/>
-    <col min="37" max="37" width="53.453125" customWidth="1"/>
-    <col min="38" max="38" width="38.6328125" customWidth="1"/>
-    <col min="39" max="39" width="32.90625" customWidth="1"/>
-    <col min="40" max="40" width="41.81640625" customWidth="1"/>
-    <col min="41" max="41" width="35.26953125" customWidth="1"/>
-    <col min="42" max="42" width="38.6328125" customWidth="1"/>
+    <col min="29" max="29" width="33.5703125" customWidth="1"/>
+    <col min="30" max="30" width="37.140625" customWidth="1"/>
+    <col min="31" max="31" width="38.140625" customWidth="1"/>
+    <col min="32" max="32" width="36.85546875" customWidth="1"/>
+    <col min="33" max="33" width="49.28515625" customWidth="1"/>
+    <col min="34" max="34" width="42.42578125" customWidth="1"/>
+    <col min="35" max="35" width="34.140625" customWidth="1"/>
+    <col min="36" max="36" width="38.140625" customWidth="1"/>
+    <col min="37" max="37" width="53.42578125" customWidth="1"/>
+    <col min="38" max="38" width="38.5703125" customWidth="1"/>
+    <col min="39" max="39" width="32.85546875" customWidth="1"/>
+    <col min="40" max="40" width="41.85546875" customWidth="1"/>
+    <col min="41" max="41" width="35.28515625" customWidth="1"/>
+    <col min="42" max="42" width="38.5703125" customWidth="1"/>
     <col min="43" max="43" width="41" customWidth="1"/>
-    <col min="44" max="44" width="38.36328125" customWidth="1"/>
-    <col min="45" max="45" width="37.36328125" customWidth="1"/>
-    <col min="46" max="46" width="29.90625" customWidth="1"/>
-    <col min="47" max="47" width="28.7265625" customWidth="1"/>
+    <col min="44" max="44" width="38.42578125" customWidth="1"/>
+    <col min="45" max="45" width="37.42578125" customWidth="1"/>
+    <col min="46" max="46" width="29.85546875" customWidth="1"/>
+    <col min="47" max="47" width="28.7109375" customWidth="1"/>
     <col min="48" max="48" width="40" customWidth="1"/>
-    <col min="49" max="49" width="33.08984375" customWidth="1"/>
-    <col min="50" max="50" width="38.1796875" customWidth="1"/>
-    <col min="51" max="51" width="8.7265625" customWidth="1"/>
+    <col min="49" max="49" width="33.140625" customWidth="1"/>
+    <col min="50" max="50" width="38.140625" customWidth="1"/>
+    <col min="51" max="51" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="AX1" s="4" t="s">
-        <v>257</v>
-      </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>50</v>
@@ -1689,7 +1689,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1" t="s">
@@ -1835,7 +1835,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="1" t="s">
@@ -1981,7 +1981,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="1" t="s">
@@ -2127,7 +2127,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
@@ -2273,7 +2273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1" t="s">
@@ -2421,7 +2421,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1" t="s">
@@ -2569,7 +2569,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>170</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>189</v>
       </c>
